--- a/erp-server/erp-server-wms/src/main/resources/excel/aliexpressDeliveryExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/aliexpressDeliveryExport.xlsx
@@ -1070,69 +1070,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="Q1:W2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="14.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="2" customWidth="1"/>
-    <col min="8" max="13" width="30.625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14.75" style="2" customWidth="1"/>
-    <col min="15" max="21" width="27" style="2" customWidth="1"/>
-    <col min="22" max="22" width="22.375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="24.375" style="2" customWidth="1"/>
-    <col min="24" max="25" width="21.125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="21" style="2" customWidth="1"/>
-    <col min="27" max="29" width="20.625" style="2" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="2"/>
+    <col min="1" max="5" width="27" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.375" style="2" customWidth="1"/>
+    <col min="8" max="9" width="21.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21" style="2" customWidth="1"/>
+    <col min="11" max="13" width="20.625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="17:23">
-      <c r="Q1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="17:23">
-      <c r="Q2" s="4" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/aliexpressDeliveryExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/aliexpressDeliveryExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>平台订单号</t>
   </si>
@@ -44,6 +44,15 @@
     <t>物流跟踪号</t>
   </si>
   <si>
+    <t>平台SKU</t>
+  </si>
+  <si>
+    <t>系统SKU</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
     <t>订单创建时间</t>
   </si>
   <si>
@@ -63,6 +72,15 @@
   </si>
   <si>
     <t>{.trackNo}</t>
+  </si>
+  <si>
+    <t>{.platformSku}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
   </si>
   <si>
     <t>{.tradeCreateTime}</t>
@@ -1070,19 +1088,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="5" width="27" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.375" style="2" customWidth="1"/>
-    <col min="8" max="9" width="21.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21" style="2" customWidth="1"/>
-    <col min="11" max="13" width="20.625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="1" max="8" width="27" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="24.375" style="2" customWidth="1"/>
+    <col min="11" max="12" width="21.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21" style="2" customWidth="1"/>
+    <col min="14" max="16" width="20.625" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1104,28 +1122,46 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
